--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>113079251</v>
       </c>
       <c r="B6" t="n">
-        <v>56910</v>
+        <v>56911</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,6 +1231,312 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120335974</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Melsbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>766806</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7097994</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Wilma Hedberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Wilma Hedberg, Martine Omark, Emma Högdahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120335979</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Melsbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>766708</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7098098</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Wilma Hedberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Wilma Hedberg, Martine Omark, Emma Högdahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120335972</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Melsbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>766902</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7098014</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Wilma Hedberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Wilma Hedberg, Martine Omark, Emma Högdahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335974</v>
+        <v>120335972</v>
       </c>
       <c r="B7" t="n">
         <v>90598</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766806</v>
+        <v>766902</v>
       </c>
       <c r="R7" t="n">
-        <v>7097994</v>
+        <v>7098014</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335972</v>
+        <v>120335974</v>
       </c>
       <c r="B9" t="n">
         <v>90598</v>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>766902</v>
+        <v>766806</v>
       </c>
       <c r="R9" t="n">
-        <v>7098014</v>
+        <v>7097994</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335972</v>
+        <v>120335979</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766902</v>
+        <v>766708</v>
       </c>
       <c r="R7" t="n">
-        <v>7098014</v>
+        <v>7098098</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120335979</v>
+        <v>120335974</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>766708</v>
+        <v>766806</v>
       </c>
       <c r="R8" t="n">
-        <v>7098098</v>
+        <v>7097994</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335974</v>
+        <v>120335972</v>
       </c>
       <c r="B9" t="n">
         <v>90598</v>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>766806</v>
+        <v>766902</v>
       </c>
       <c r="R9" t="n">
-        <v>7097994</v>
+        <v>7098014</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335979</v>
+        <v>120335972</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766708</v>
+        <v>766902</v>
       </c>
       <c r="R7" t="n">
-        <v>7098098</v>
+        <v>7098014</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335972</v>
+        <v>120335979</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>766902</v>
+        <v>766708</v>
       </c>
       <c r="R9" t="n">
-        <v>7098014</v>
+        <v>7098098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 38314-2020 artfynd.xlsx
+++ b/artfynd/A 38314-2020 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120335972</v>
+        <v>120335979</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766902</v>
+        <v>766708</v>
       </c>
       <c r="R7" t="n">
-        <v>7098014</v>
+        <v>7098098</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120335979</v>
+        <v>120335972</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>766708</v>
+        <v>766902</v>
       </c>
       <c r="R9" t="n">
-        <v>7098098</v>
+        <v>7098014</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
